--- a/runs/RELX/2026-10-14/bear/scratch/g_rf_fred_aug/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_rf_fred_aug/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2082.960423917025</v>
+        <v>2142.239837245387</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.09853100000000001</v>
+        <v>0.0907478</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09153044827456001</v>
+        <v>0.08474489885056001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11244.75989545621</v>
+        <v>11416.68988688496</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>40252.39032785742</v>
+        <v>44471.01741435959</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>27141.28019145097</v>
+        <v>30839.1778278744</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>38386.04008690717</v>
+        <v>42255.86771475936</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>31389.04008690717</v>
+        <v>35258.86771475936</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>30514.3680801783</v>
+        <v>34469.03807475809</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>17.4992317484214</v>
+        <v>19.76713670853211</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1749.92317484214</v>
+        <v>1976.713670853211</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.3684867648</v>
+        <v>-0.2866424862</v>
       </c>
     </row>
   </sheetData>
